--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ23" headerRowCount="1">
-  <autoFilter ref="A1:CQ23"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR24" headerRowCount="1">
+  <autoFilter ref="A1:CR24"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$23)</f>
+        <f>COUNTA('Picks'!$A$2:$A$24)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$24,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$24,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")/(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$24)/SUM('Picks'!$BX$2:$BX$24),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$23)</f>
+        <f>SUM('Picks'!$BY$2:$BY$24)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$24,"&lt;&gt;",'Picks'!$AB$2:$AB$24),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$24,'Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ23"/>
+  <dimension ref="A1:CR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1879,6 +1886,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2170,6 +2178,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2461,6 +2470,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2748,6 +2758,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3039,6 +3050,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3330,6 +3342,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3617,6 +3630,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3908,6 +3922,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4199,6 +4214,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4490,6 +4506,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4777,6 +4794,7 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5064,6 +5082,7 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5355,6 +5374,7 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5642,6 +5662,7 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5933,6 +5954,7 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6222,12 +6244,13 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
-      <c r="CP17" s="24" t="inlineStr">
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
         <is>
           <t>0.643489</t>
         </is>
       </c>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6521,12 +6544,13 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
-      <c r="CP18" s="24" t="inlineStr">
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
         <is>
           <t>0.57112</t>
         </is>
       </c>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6820,12 +6844,13 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
-      <c r="CP19" s="24" t="inlineStr">
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="inlineStr">
         <is>
           <t>0.758559</t>
         </is>
       </c>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7119,12 +7144,13 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
-      <c r="CP20" s="24" t="inlineStr">
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="inlineStr">
         <is>
           <t>0.772803</t>
         </is>
       </c>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7414,12 +7440,13 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="inlineStr">
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
         <is>
           <t>0.51407</t>
         </is>
       </c>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7709,12 +7736,13 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="inlineStr">
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="inlineStr">
         <is>
           <t>0.668225</t>
         </is>
       </c>
-      <c r="CQ22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8008,14 +8036,301 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="inlineStr">
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="inlineStr">
         <is>
           <t>0.580877</t>
         </is>
       </c>
-      <c r="CQ23" s="24" t="inlineStr">
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>56579ecb47384a41</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:42.290404Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.774468</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>-0.105484</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.1055.</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:25.832875Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN24" s="28" t="n">
+        <v>0.871287</v>
+      </c>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="inlineStr">
+        <is>
+          <t>0.9026326565</t>
+        </is>
+      </c>
+      <c r="CD24" s="24" t="inlineStr">
+        <is>
+          <t>2.972439</t>
+        </is>
+      </c>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="inlineStr">
+        <is>
+          <t>1.230079</t>
+        </is>
+      </c>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="CR24" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR24" headerRowCount="1">
-  <autoFilter ref="A1:CR24"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS24" headerRowCount="1">
+  <autoFilter ref="A1:CS24"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR24"/>
+  <dimension ref="A1:CS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1887,6 +1894,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2179,6 +2187,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2471,6 +2480,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2759,6 +2769,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3051,6 +3062,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3343,6 +3355,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3631,6 +3644,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3923,6 +3937,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4215,6 +4230,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4507,6 +4523,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4795,6 +4812,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5083,6 +5101,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5375,6 +5394,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5663,6 +5683,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5955,6 +5976,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6245,12 +6267,13 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>0.643489</t>
         </is>
       </c>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6545,12 +6568,13 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>0.57112</t>
         </is>
       </c>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6845,12 +6869,13 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>0.758559</t>
         </is>
       </c>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7145,12 +7170,13 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>0.772803</t>
         </is>
       </c>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7441,12 +7467,13 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
         <is>
           <t>0.51407</t>
         </is>
       </c>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7737,12 +7764,13 @@
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="inlineStr">
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
         <is>
           <t>0.668225</t>
         </is>
       </c>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8037,12 +8065,13 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="inlineStr">
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>0.580877</t>
         </is>
       </c>
-      <c r="CR23" s="24" t="inlineStr">
+      <c r="CS23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8051,12 +8080,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>56579ecb47384a41</t>
+          <t>b032a529741d4d83</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -8262,7 +8291,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:25.832875Z</t>
+          <t>2026-08-04T14:23:15.869749Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8323,12 +8352,13 @@
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="inlineStr">
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="inlineStr">
         <is>
           <t>0.774468</t>
         </is>
       </c>
-      <c r="CR24" s="24" t="inlineStr">
+      <c r="CS24" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS24" headerRowCount="1">
-  <autoFilter ref="A1:CS24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS28" headerRowCount="1">
+  <autoFilter ref="A1:CS28"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$24)</f>
+        <f>COUNTA('Picks'!$A$2:$A$28)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$24,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$28,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$24,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$28,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")/(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")/(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$24)/SUM('Picks'!$BX$2:$BX$24),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$28)/SUM('Picks'!$BX$2:$BX$28),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$24)</f>
+        <f>SUM('Picks'!$BY$2:$BY$28)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$24,"&lt;&gt;",'Picks'!$AB$2:$AB$24),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$28,"&lt;&gt;",'Picks'!$AB$2:$AB$28),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$24,'Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$28,'Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS24"/>
+  <dimension ref="A1:CS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8080,12 +8080,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>b032a529741d4d83</t>
+          <t>9fb18a9d55ab4afe</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:24:46.511596Z</t>
+          <t>2026-08-05T01:07:48.070985Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -8130,20 +8130,20 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="O24" s="28" t="n">
         <v>0.774468</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>-0.105484</v>
+        <v>-0.085476</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>0</v>
@@ -8158,21 +8158,35 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:32.559583Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.1055.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8600 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.0855.</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8291,7 +8305,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:15.869749Z</t>
+          <t>2026-08-05T01:07:13.594446Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8301,16 +8315,16 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="BN24" s="28" t="n">
-        <v>0.871287</v>
+        <v>0.851485</v>
       </c>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
@@ -8364,6 +8378,1162 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>ac592d8716954baa</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.660664</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6600 (aec-wnba-phx-atl-2026-08-05); model edge vs ask +0.0007.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:03.119408Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN25" s="28" t="n">
+        <v>0.653465</v>
+      </c>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="inlineStr">
+        <is>
+          <t>0.708542691</t>
+        </is>
+      </c>
+      <c r="CD25" s="24" t="inlineStr">
+        <is>
+          <t>-1.788883</t>
+        </is>
+      </c>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="inlineStr">
+        <is>
+          <t>-1.7391</t>
+        </is>
+      </c>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>690c7ebf845c4158</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.741322</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>-0.048594</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0487.</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:04.100169Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="BN26" s="28" t="n">
+        <v>0.782178</v>
+      </c>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="inlineStr">
+        <is>
+          <t>0.8394756417</t>
+        </is>
+      </c>
+      <c r="CD26" s="24" t="inlineStr">
+        <is>
+          <t>0.315883</t>
+        </is>
+      </c>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="inlineStr">
+        <is>
+          <t>1.520421</t>
+        </is>
+      </c>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>335fc0ed739647c0</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.532764</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.0574</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5900 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0572. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:04.826877Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN27" s="28" t="n">
+        <v>0.584158</v>
+      </c>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="inlineStr">
+        <is>
+          <t>0.4611418469</t>
+        </is>
+      </c>
+      <c r="CD27" s="24" t="inlineStr">
+        <is>
+          <t>1.287558</t>
+        </is>
+      </c>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="CJ27" s="24" t="inlineStr">
+        <is>
+          <t>-1.305803</t>
+        </is>
+      </c>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>3b0366a9f4b14eb1</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.549529</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>-0.009941999999999999</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0105. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:05.642651Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN28" s="28" t="n">
+        <v>0.554455</v>
+      </c>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="inlineStr">
+        <is>
+          <t>0.573492291</t>
+        </is>
+      </c>
+      <c r="CD28" s="24" t="inlineStr">
+        <is>
+          <t>3.024749</t>
+        </is>
+      </c>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="CJ28" s="24" t="inlineStr">
+        <is>
+          <t>2.235061</t>
+        </is>
+      </c>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -8381,12 +8381,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>ac592d8716954baa</t>
+          <t>4c0d89bc92004030</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:03.119408Z</t>
+          <t>2026-08-05T13:52:33.816980Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8668,12 +8668,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>690c7ebf845c4158</t>
+          <t>2173692b5b9f401b</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8718,23 +8718,23 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-376</v>
+        <v>-335</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.265957</v>
+        <v>1.298507</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.789916</v>
+        <v>0.770115</v>
       </c>
       <c r="O26" s="28" t="n">
         <v>0.741322</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.048594</v>
+        <v>-0.028793</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>2</v>
@@ -8760,7 +8760,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0487.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7700 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0287.</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:04.100169Z</t>
+          <t>2026-08-05T13:52:34.422318Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8889,16 +8889,16 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-376</v>
+        <v>-335</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.265957</v>
+        <v>1.298507</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.789916</v>
+        <v>0.770115</v>
       </c>
       <c r="BN26" s="28" t="n">
-        <v>0.782178</v>
+        <v>0.7623760000000001</v>
       </c>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
@@ -8955,12 +8955,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>335fc0ed739647c0</t>
+          <t>a1c1b7b1ec1d4431</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -9005,23 +9005,23 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-144</v>
+        <v>-133</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.75188</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.570815</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.532764</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.0574</v>
+        <v>-0.038051</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1</v>
@@ -9047,7 +9047,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5900 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0572. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0372. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:04.826877Z</t>
+          <t>2026-08-05T13:52:34.867255Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9176,16 +9176,16 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-144</v>
+        <v>-133</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.75188</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.570815</v>
       </c>
       <c r="BN27" s="28" t="n">
-        <v>0.584158</v>
+        <v>0.564356</v>
       </c>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
@@ -9246,12 +9246,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>3b0366a9f4b14eb1</t>
+          <t>e20b6561ab4849f5</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9296,23 +9296,23 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O28" s="28" t="n">
         <v>0.549529</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>-0.009941999999999999</v>
+        <v>-0.021286</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="S28" s="29" t="n">
         <v>1</v>
@@ -9338,7 +9338,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0105. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0205. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:05.642651Z</t>
+          <t>2026-08-05T13:52:35.451044Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9467,16 +9467,16 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN28" s="28" t="n">
-        <v>0.554455</v>
+        <v>0.564356</v>
       </c>
       <c r="BO28" s="28" t="n"/>
       <c r="BP28" s="25" t="n"/>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS28" headerRowCount="1">
-  <autoFilter ref="A1:CS28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS34" headerRowCount="1">
+  <autoFilter ref="A1:CS34"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$28)</f>
+        <f>COUNTA('Picks'!$A$2:$A$34)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$28,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$34,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$34,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"win")+COUNTIFS('Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$28,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$34,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$34,"&gt;0",'Picks'!$V$2:$V$34,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$34,"&gt;0",'Picks'!$V$2:$V$34,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")/(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$34,"&gt;0",'Picks'!$V$2:$V$34,"win")/(COUNTIFS('Picks'!$BX$2:$BX$34,"&gt;0",'Picks'!$V$2:$V$34,"win")+COUNTIFS('Picks'!$BX$2:$BX$34,"&gt;0",'Picks'!$V$2:$V$34,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$28)/SUM('Picks'!$BX$2:$BX$28),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$34)/SUM('Picks'!$BX$2:$BX$34),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$28)</f>
+        <f>SUM('Picks'!$BY$2:$BY$34)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$28,"&lt;&gt;",'Picks'!$AB$2:$AB$28),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$34,"&lt;&gt;",'Picks'!$AB$2:$AB$34),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$34,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$34,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$28,'Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$34,'Picks'!$AM$2:$AM$34,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A14,'Picks'!$U$2:$U$34,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A14,'Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A14,'Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$34,'Picks'!$H$2:$H$34,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$34,'Picks'!$H$2:$H$34,$A14,'Picks'!$U$2:$U$34,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A15,'Picks'!$U$2:$U$34,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A15,'Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A15,'Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$34,'Picks'!$H$2:$H$34,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$34,'Picks'!$H$2:$H$34,$A15,'Picks'!$U$2:$U$34,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A16,'Picks'!$U$2:$U$34,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A16,'Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$34,$A16,'Picks'!$U$2:$U$34,"settled",'Picks'!$V$2:$V$34,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$34,'Picks'!$H$2:$H$34,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$34,'Picks'!$H$2:$H$34,$A16,'Picks'!$U$2:$U$34,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS28"/>
+  <dimension ref="A1:CS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8381,12 +8381,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>4c0d89bc92004030</t>
+          <t>fcb554e501db41f7</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-05T21:01:20.386769Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8431,26 +8431,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-194</v>
+        <v>-233</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.429185</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.6997</v>
       </c>
       <c r="O25" s="28" t="n">
         <v>0.660664</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.0008</v>
+        <v>-0.039036</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8459,21 +8459,35 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>96</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:55.924337Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.6600 (aec-wnba-phx-atl-2026-08-05); model edge vs ask +0.0007.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-phx-atl-2026-08-05); model edge vs ask -0.0393.</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8491,7 +8505,7 @@
       <c r="AJ25" s="31" t="n"/>
       <c r="AK25" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL25" s="26" t="n">
@@ -8499,17 +8513,17 @@
       </c>
       <c r="AM25" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN25" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO25" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP25" s="24" t="inlineStr">
@@ -8592,7 +8606,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:33.816980Z</t>
+          <t>2026-08-05T21:00:50.745854Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8602,16 +8616,16 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-194</v>
+        <v>-233</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.429185</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.6997</v>
       </c>
       <c r="BN25" s="28" t="n">
-        <v>0.653465</v>
+        <v>0.693069</v>
       </c>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
@@ -8661,19 +8675,19 @@
       </c>
       <c r="CS25" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>2173692b5b9f401b</t>
+          <t>756ccd778ac2469e</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-05T21:01:20.386769Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8737,7 +8751,7 @@
         <v>9</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8746,18 +8760,32 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:56.598669Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.7700 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0287.</t>
@@ -8778,7 +8806,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8786,17 +8814,17 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
@@ -8879,7 +8907,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:34.422318Z</t>
+          <t>2026-08-05T21:00:51.572136Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8955,12 +8983,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>a1c1b7b1ec1d4431</t>
+          <t>fbae16fd793f4cb6</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-05T21:01:20.386769Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -9005,26 +9033,26 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.854701</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.539171</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.532764</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.038051</v>
+        <v>-0.006407</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -9033,21 +9061,35 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>96</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:57.279339Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0372. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5400 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0072.</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -9057,7 +9099,7 @@
       </c>
       <c r="AG27" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH27" s="24" t="n"/>
@@ -9065,7 +9107,7 @@
       <c r="AJ27" s="31" t="n"/>
       <c r="AK27" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL27" s="26" t="n">
@@ -9073,17 +9115,17 @@
       </c>
       <c r="AM27" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN27" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO27" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP27" s="24" t="inlineStr">
@@ -9166,7 +9208,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:34.867255Z</t>
+          <t>2026-08-05T21:00:52.092163Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9176,16 +9218,16 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.854701</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.539171</v>
       </c>
       <c r="BN27" s="28" t="n">
-        <v>0.564356</v>
+        <v>0.534653</v>
       </c>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
@@ -9215,11 +9257,7 @@
       <c r="CF27" s="24" t="n"/>
       <c r="CG27" s="24" t="n"/>
       <c r="CH27" s="24" t="n"/>
-      <c r="CI27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
-        </is>
-      </c>
+      <c r="CI27" s="24" t="n"/>
       <c r="CJ27" s="24" t="inlineStr">
         <is>
           <t>-1.305803</t>
@@ -9246,12 +9284,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>e20b6561ab4849f5</t>
+          <t>4c120856e1e94f85</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-06T00:23:10.436172Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9315,7 +9353,7 @@
         <v>13</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -9324,21 +9362,35 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>95</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:26:39.722755Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0205. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0205. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9356,7 +9408,7 @@
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL28" s="26" t="n">
@@ -9364,17 +9416,17 @@
       </c>
       <c r="AM28" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN28" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO28" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP28" s="24" t="inlineStr">
@@ -9457,7 +9509,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:35.451044Z</t>
+          <t>2026-08-06T00:22:59.513151Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9508,7 +9560,7 @@
       <c r="CH28" s="24" t="n"/>
       <c r="CI28" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
         </is>
       </c>
       <c r="CJ28" s="24" t="inlineStr">
@@ -9531,6 +9583,1786 @@
       <c r="CS28" s="24" t="inlineStr">
         <is>
           <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>85909d8c00894246</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:18.495512Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>401857119</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.555661</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.045857</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:32.192371Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5100 (aec-wnba-lv-ind-2026-08-06); model edge vs ask +0.0457. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-ind</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>ee263665aa5e3903</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:56.303091Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN29" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="inlineStr">
+        <is>
+          <t>0.5778273332</t>
+        </is>
+      </c>
+      <c r="CD29" s="24" t="inlineStr">
+        <is>
+          <t>4.392054</t>
+        </is>
+      </c>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ29" s="24" t="inlineStr">
+        <is>
+          <t>-4.728134</t>
+        </is>
+      </c>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="inlineStr">
+        <is>
+          <t>0.555661</t>
+        </is>
+      </c>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>7d69846638e04c11</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:18.495512Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>401857120</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.086957</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.7758</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:32.598784Z</t>
+        </is>
+      </c>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.9200 (aec-wnba-la-min-2026-08-06); model edge vs ask -0.1442. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>41c5f8278a71f705</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:57.071624Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.086957</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BN30" s="28" t="n">
+        <v>0.910891</v>
+      </c>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="inlineStr">
+        <is>
+          <t>0.904420571</t>
+        </is>
+      </c>
+      <c r="CD30" s="24" t="inlineStr">
+        <is>
+          <t>3.215406</t>
+        </is>
+      </c>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ30" s="24" t="inlineStr">
+        <is>
+          <t>-0.02251</t>
+        </is>
+      </c>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="inlineStr">
+        <is>
+          <t>0.7758</t>
+        </is>
+      </c>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>17f439c082b14660</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:18.495512Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>401857121</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.617434</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.037602</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>83</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:33.053227Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5800 (aec-wnba-tor-por-2026-08-06); model edge vs ask +0.0374. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-por</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>90fd0d58822b7917</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:57.472055Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN31" s="28" t="n">
+        <v>0.574257</v>
+      </c>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="inlineStr">
+        <is>
+          <t>0.6630193028</t>
+        </is>
+      </c>
+      <c r="CD31" s="24" t="inlineStr">
+        <is>
+          <t>4.186942</t>
+        </is>
+      </c>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ31" s="24" t="inlineStr">
+        <is>
+          <t>-0.197354</t>
+        </is>
+      </c>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="inlineStr">
+        <is>
+          <t>0.617434</t>
+        </is>
+      </c>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>ccd7cb9f5a3b4dc4</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:21:40.990328Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>401857122</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.5232869999999999</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>-0.176413</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-phx-conn-2026-08-07); model edge vs ask -0.1767. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-con</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>0cc51532bda1a1e7</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:38.985847Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN32" s="28" t="n">
+        <v>0.693069</v>
+      </c>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="inlineStr">
+        <is>
+          <t>0.464766751</t>
+        </is>
+      </c>
+      <c r="CD32" s="24" t="inlineStr">
+        <is>
+          <t>-5.674273</t>
+        </is>
+      </c>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ32" s="24" t="inlineStr">
+        <is>
+          <t>5.627573</t>
+        </is>
+      </c>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="inlineStr">
+        <is>
+          <t>0.523287</t>
+        </is>
+      </c>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>69328c0091e64b00</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:21:40.990328Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.561972</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.221836</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.3400 (aec-wnba-atl-wsh-2026-08-07); model edge vs ask +0.2220.</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:39.610102Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN33" s="28" t="n">
+        <v>0.336634</v>
+      </c>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="inlineStr">
+        <is>
+          <t>0.5839932663</t>
+        </is>
+      </c>
+      <c r="CD33" s="24" t="inlineStr">
+        <is>
+          <t>-1.592597</t>
+        </is>
+      </c>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="inlineStr">
+        <is>
+          <t>6.900454</t>
+        </is>
+      </c>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>79c011137f884b79</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:21:40.990328Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>401857124</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.506578</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.006578</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5000 (aec-wnba-gsv-dal-2026-08-07); model edge vs ask +0.0066.</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>c2d3c7c45366cc37</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:40.170846Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN34" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="inlineStr">
+        <is>
+          <t>0.4936041743</t>
+        </is>
+      </c>
+      <c r="CD34" s="24" t="inlineStr">
+        <is>
+          <t>-0.766561</t>
+        </is>
+      </c>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="inlineStr">
+        <is>
+          <t>2.335261</t>
+        </is>
+      </c>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="inlineStr">
+        <is>
+          <t>0.506578</t>
+        </is>
+      </c>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -10504,12 +10504,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>ccd7cb9f5a3b4dc4</t>
+          <t>20bdbfe22d1b4bb6</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:21:40.990328Z</t>
+          <t>2026-08-07T18:28:49.432084Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:38.985847Z</t>
+          <t>2026-08-07T18:28:02.520228Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10795,12 +10795,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>69328c0091e64b00</t>
+          <t>06246ff3dc9f4c64</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:21:40.990328Z</t>
+          <t>2026-08-07T18:28:49.432084Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:39.610102Z</t>
+          <t>2026-08-07T18:28:03.051036Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -11082,12 +11082,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>79c011137f884b79</t>
+          <t>d6adbdb873ef4965</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:21:40.990328Z</t>
+          <t>2026-08-07T18:28:49.432084Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -11132,23 +11132,23 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.5</v>
+        <v>0.490196</v>
       </c>
       <c r="O34" s="28" t="n">
         <v>0.506578</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.006578</v>
+        <v>0.016382</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="S34" s="29" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5000 (aec-wnba-gsv-dal-2026-08-07); model edge vs ask +0.0066.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.4900 (aec-wnba-gsv-dal-2026-08-07); model edge vs ask +0.0166.</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:40.170846Z</t>
+          <t>2026-08-07T18:28:03.748682Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -11303,16 +11303,16 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.5</v>
+        <v>0.490196</v>
       </c>
       <c r="BN34" s="28" t="n">
-        <v>0.49505</v>
+        <v>0.485149</v>
       </c>
       <c r="BO34" s="28" t="n"/>
       <c r="BP34" s="25" t="n"/>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS24" headerRowCount="1">
-  <autoFilter ref="A1:CS24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS48" headerRowCount="1">
+  <autoFilter ref="A1:CS48"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$24)</f>
+        <f>COUNTA('Picks'!$A$2:$A$48)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$24,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$24,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$48,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")/(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")/(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$24)/SUM('Picks'!$BX$2:$BX$24),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$48)/SUM('Picks'!$BX$2:$BX$48),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$24)</f>
+        <f>SUM('Picks'!$BY$2:$BY$48)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$24,"&lt;&gt;",'Picks'!$AB$2:$AB$24),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$48,"&lt;&gt;",'Picks'!$AB$2:$AB$48),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$24,'Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$48,'Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS24"/>
+  <dimension ref="A1:CS48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8080,12 +8080,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>b032a529741d4d83</t>
+          <t>9fb18a9d55ab4afe</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:24:46.511596Z</t>
+          <t>2026-08-05T01:07:48.070985Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -8130,20 +8130,20 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="O24" s="28" t="n">
         <v>0.774468</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>-0.105484</v>
+        <v>-0.085476</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>0</v>
@@ -8158,21 +8158,35 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:32.559583Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.1055.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8600 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.0855.</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8291,7 +8305,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:15.869749Z</t>
+          <t>2026-08-05T01:07:13.594446Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8301,16 +8315,16 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="BN24" s="28" t="n">
-        <v>0.871287</v>
+        <v>0.851485</v>
       </c>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
@@ -8364,6 +8378,7248 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>fcb554e501db41f7</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:01:20.386769Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.660664</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>-0.039036</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:55.924337Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-phx-atl-2026-08-05); model edge vs ask -0.0393.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:50.745854Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN25" s="28" t="n">
+        <v>0.693069</v>
+      </c>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="inlineStr">
+        <is>
+          <t>0.708542691</t>
+        </is>
+      </c>
+      <c r="CD25" s="24" t="inlineStr">
+        <is>
+          <t>-1.788883</t>
+        </is>
+      </c>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="inlineStr">
+        <is>
+          <t>-1.7391</t>
+        </is>
+      </c>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>756ccd778ac2469e</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:01:20.386769Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-335</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.298507</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.770115</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.741322</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>-0.028793</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:56.598669Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7700 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0287.</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:51.572136Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-335</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.298507</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.770115</v>
+      </c>
+      <c r="BN26" s="28" t="n">
+        <v>0.7623760000000001</v>
+      </c>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="inlineStr">
+        <is>
+          <t>0.8394756417</t>
+        </is>
+      </c>
+      <c r="CD26" s="24" t="inlineStr">
+        <is>
+          <t>0.315883</t>
+        </is>
+      </c>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="inlineStr">
+        <is>
+          <t>1.520421</t>
+        </is>
+      </c>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>fbae16fd793f4cb6</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:01:20.386769Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.532764</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.006407</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:57.279339Z</t>
+        </is>
+      </c>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5400 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0072.</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:52.092163Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN27" s="28" t="n">
+        <v>0.534653</v>
+      </c>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="inlineStr">
+        <is>
+          <t>0.4611418469</t>
+        </is>
+      </c>
+      <c r="CD27" s="24" t="inlineStr">
+        <is>
+          <t>1.287558</t>
+        </is>
+      </c>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="inlineStr">
+        <is>
+          <t>-1.305803</t>
+        </is>
+      </c>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>4c120856e1e94f85</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:23:10.436172Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.549529</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>-0.021286</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:26:39.722755Z</t>
+        </is>
+      </c>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0205. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:59.513151Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN28" s="28" t="n">
+        <v>0.564356</v>
+      </c>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="inlineStr">
+        <is>
+          <t>0.573492291</t>
+        </is>
+      </c>
+      <c r="CD28" s="24" t="inlineStr">
+        <is>
+          <t>3.024749</t>
+        </is>
+      </c>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ28" s="24" t="inlineStr">
+        <is>
+          <t>2.235061</t>
+        </is>
+      </c>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>85909d8c00894246</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:18.495512Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>401857119</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.555661</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.045857</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:32.192371Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5100 (aec-wnba-lv-ind-2026-08-06); model edge vs ask +0.0457. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-ind</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>ee263665aa5e3903</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:56.303091Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN29" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="inlineStr">
+        <is>
+          <t>0.5778273332</t>
+        </is>
+      </c>
+      <c r="CD29" s="24" t="inlineStr">
+        <is>
+          <t>4.392054</t>
+        </is>
+      </c>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ29" s="24" t="inlineStr">
+        <is>
+          <t>-4.728134</t>
+        </is>
+      </c>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="inlineStr">
+        <is>
+          <t>0.555661</t>
+        </is>
+      </c>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>7d69846638e04c11</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:18.495512Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>401857120</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.086957</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.7758</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:32.598784Z</t>
+        </is>
+      </c>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.9200 (aec-wnba-la-min-2026-08-06); model edge vs ask -0.1442. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>41c5f8278a71f705</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:57.071624Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.086957</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BN30" s="28" t="n">
+        <v>0.910891</v>
+      </c>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="inlineStr">
+        <is>
+          <t>0.904420571</t>
+        </is>
+      </c>
+      <c r="CD30" s="24" t="inlineStr">
+        <is>
+          <t>3.215406</t>
+        </is>
+      </c>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ30" s="24" t="inlineStr">
+        <is>
+          <t>-0.02251</t>
+        </is>
+      </c>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="inlineStr">
+        <is>
+          <t>0.7758</t>
+        </is>
+      </c>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>17f439c082b14660</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:18.495512Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>401857121</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.617434</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.037602</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>83</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:33.053227Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5800 (aec-wnba-tor-por-2026-08-06); model edge vs ask +0.0374. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-por</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>90fd0d58822b7917</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:57.472055Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN31" s="28" t="n">
+        <v>0.574257</v>
+      </c>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="inlineStr">
+        <is>
+          <t>0.6630193028</t>
+        </is>
+      </c>
+      <c r="CD31" s="24" t="inlineStr">
+        <is>
+          <t>4.186942</t>
+        </is>
+      </c>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ31" s="24" t="inlineStr">
+        <is>
+          <t>-0.197354</t>
+        </is>
+      </c>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="inlineStr">
+        <is>
+          <t>0.617434</t>
+        </is>
+      </c>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>37898ae8bd4a4c61</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:24.360448Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>401857122</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.5232869999999999</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>-0.167115</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:03:23.983838Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6900 (aec-wnba-phx-conn-2026-08-07); model edge vs ask -0.1667. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-con</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>0cc51532bda1a1e7</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:55:59.492580Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN32" s="28" t="n">
+        <v>0.683168</v>
+      </c>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="inlineStr">
+        <is>
+          <t>0.464766751</t>
+        </is>
+      </c>
+      <c r="CD32" s="24" t="inlineStr">
+        <is>
+          <t>-5.674273</t>
+        </is>
+      </c>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ32" s="24" t="inlineStr">
+        <is>
+          <t>5.627573</t>
+        </is>
+      </c>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="inlineStr">
+        <is>
+          <t>0.523287</t>
+        </is>
+      </c>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>81a2663931b24d74</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:24.360448Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.561972</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.221836</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:03:24.422459Z</t>
+        </is>
+      </c>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.3400 (aec-wnba-atl-wsh-2026-08-07); model edge vs ask +0.2220.</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:00.000131Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN33" s="28" t="n">
+        <v>0.336634</v>
+      </c>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="inlineStr">
+        <is>
+          <t>0.5839932663</t>
+        </is>
+      </c>
+      <c r="CD33" s="24" t="inlineStr">
+        <is>
+          <t>-1.592597</t>
+        </is>
+      </c>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="inlineStr">
+        <is>
+          <t>6.900454</t>
+        </is>
+      </c>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>ce8b7cfa0d84414d</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T01:00:54.678171Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>401857124</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.506578</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.016382</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:03:56.240853Z</t>
+        </is>
+      </c>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.4900 (aec-wnba-gsv-dal-2026-08-07); model edge vs ask +0.0166.</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>c2d3c7c45366cc37</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T01:00:45.249760Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN34" s="28" t="n">
+        <v>0.485149</v>
+      </c>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="inlineStr">
+        <is>
+          <t>0.4936041743</t>
+        </is>
+      </c>
+      <c r="CD34" s="24" t="inlineStr">
+        <is>
+          <t>-0.766561</t>
+        </is>
+      </c>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="inlineStr">
+        <is>
+          <t>2.335261</t>
+        </is>
+      </c>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="inlineStr">
+        <is>
+          <t>0.506578</t>
+        </is>
+      </c>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>4f17191a6c83414d</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:59.410253Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T15:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>401857126</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.642496</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>-0.047906</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:12:53.839909Z</t>
+        </is>
+      </c>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6900 (aec-wnba-ind-chi-2026-08-08); model edge vs ask -0.0475. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>wnba-ind</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>151c56cfebdd36b1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:41.075858Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN35" s="28" t="n">
+        <v>0.683168</v>
+      </c>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="inlineStr">
+        <is>
+          <t>0.3173646589</t>
+        </is>
+      </c>
+      <c r="CD35" s="24" t="inlineStr">
+        <is>
+          <t>0.612216</t>
+        </is>
+      </c>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ35" s="24" t="inlineStr">
+        <is>
+          <t>1.718569</t>
+        </is>
+      </c>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="inlineStr">
+        <is>
+          <t>0.642496</t>
+        </is>
+      </c>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>34e6986747844e0e</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:59.410253Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>401857127</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.636385</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.136385</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:12:54.769320Z</t>
+        </is>
+      </c>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5000 (aec-wnba-sea-por-2026-08-08); model edge vs ask +0.1364. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>wnba-por</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>c4f4370995132da0</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:41.814320Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN36" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="inlineStr">
+        <is>
+          <t>0.6792726129</t>
+        </is>
+      </c>
+      <c r="CD36" s="24" t="inlineStr">
+        <is>
+          <t>-3.251216</t>
+        </is>
+      </c>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ36" s="24" t="inlineStr">
+        <is>
+          <t>6.663423</t>
+        </is>
+      </c>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="inlineStr">
+        <is>
+          <t>0.636385</t>
+        </is>
+      </c>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>c76fa7f043d24097</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:59:23.763456Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T12:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>401857128</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.513331</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.263331</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="X37" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:24:37.708312Z</t>
+        </is>
+      </c>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.2500 (aec-wnba-lv-ny-2026-08-09); model edge vs ask +0.2633. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>326af12f4add44d3</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:58:13.130881Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN37" s="28" t="n">
+        <v>0.247525</v>
+      </c>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="inlineStr">
+        <is>
+          <t>0.4879470816</t>
+        </is>
+      </c>
+      <c r="CD37" s="24" t="inlineStr">
+        <is>
+          <t>3.090342</t>
+        </is>
+      </c>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ37" s="24" t="inlineStr">
+        <is>
+          <t>-3.371641</t>
+        </is>
+      </c>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="inlineStr">
+        <is>
+          <t>0.513331</t>
+        </is>
+      </c>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>d31cf22d794b4e7c</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:06:21.079905Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T15:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>401857129</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.695232</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.164716</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W38" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="X38" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n">
+        <v>1.7699</v>
+      </c>
+      <c r="AD38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:29:27.139926Z</t>
+        </is>
+      </c>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5300 (aec-wnba-phx-wsh-2026-08-09); model edge vs ask +0.1652. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>28057b4491fbc31b</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:41.727182Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN38" s="28" t="n">
+        <v>0.524752</v>
+      </c>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="inlineStr">
+        <is>
+          <t>0.7723991943</t>
+        </is>
+      </c>
+      <c r="CD38" s="24" t="inlineStr">
+        <is>
+          <t>0.96982</t>
+        </is>
+      </c>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ38" s="24" t="inlineStr">
+        <is>
+          <t>6.116575</t>
+        </is>
+      </c>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="inlineStr">
+        <is>
+          <t>0.695232</t>
+        </is>
+      </c>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>194ec7af0d9549c6</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:06:21.079905Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T15:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>401857130</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.686674</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>-0.003728</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W39" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="X39" s="26" t="n">
+        <v>103</v>
+      </c>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:29:27.602016Z</t>
+        </is>
+      </c>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6900 (aec-wnba-dal-min-2026-08-09); model edge vs ask -0.0033. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>a5bf8ab17ecf7ac2</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:42.495207Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN39" s="28" t="n">
+        <v>0.683168</v>
+      </c>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="inlineStr">
+        <is>
+          <t>0.7587906514</t>
+        </is>
+      </c>
+      <c r="CD39" s="24" t="inlineStr">
+        <is>
+          <t>4.679116</t>
+        </is>
+      </c>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="CJ39" s="24" t="inlineStr">
+        <is>
+          <t>-3.292164</t>
+        </is>
+      </c>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="inlineStr">
+        <is>
+          <t>0.686674</t>
+        </is>
+      </c>
+      <c r="CS39" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>b15a97b0ddc84635</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:27:02.435009Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>401857131</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.68049</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>-0.01921</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W40" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="X40" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="AD40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T02:34:07.318931Z</t>
+        </is>
+      </c>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-gsv-la-2026-08-09); model edge vs ask -0.0195. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>3f8776ef716da556</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:42.890552Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN40" s="28" t="n">
+        <v>0.693069</v>
+      </c>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="inlineStr">
+        <is>
+          <t>0.2620546512</t>
+        </is>
+      </c>
+      <c r="CD40" s="24" t="inlineStr">
+        <is>
+          <t>1.491968</t>
+        </is>
+      </c>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ40" s="24" t="inlineStr">
+        <is>
+          <t>-1.513705</t>
+        </is>
+      </c>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="inlineStr">
+        <is>
+          <t>0.68049</t>
+        </is>
+      </c>
+      <c r="CS40" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>8d4481f7be804794</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:47.251195Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>401857132</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.737133</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>-0.142819</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="X41" s="26" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="AD41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:06:33.323693Z</t>
+        </is>
+      </c>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-atl-2026-08-10); model edge vs ask -0.1429. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>cc3e04aa2e66419b</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:14.661341Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN41" s="28" t="n">
+        <v>0.871287</v>
+      </c>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="inlineStr">
+        <is>
+          <t>0.8354799774</t>
+        </is>
+      </c>
+      <c r="CD41" s="24" t="inlineStr">
+        <is>
+          <t>3.773711</t>
+        </is>
+      </c>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ41" s="24" t="inlineStr">
+        <is>
+          <t>-3.297793</t>
+        </is>
+      </c>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="inlineStr">
+        <is>
+          <t>0.737133</t>
+        </is>
+      </c>
+      <c r="CS41" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>fbd65d4071754e79</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:47.251195Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>401857133</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.543228</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.012712</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="X42" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:06:33.815356Z</t>
+        </is>
+      </c>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5300 (aec-wnba-chi-sea-2026-08-10); model edge vs ask +0.0132.</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>0f4dad8fd6dfb442</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:14.903004Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN42" s="28" t="n">
+        <v>0.524752</v>
+      </c>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="inlineStr">
+        <is>
+          <t>0.4387952332</t>
+        </is>
+      </c>
+      <c r="CD42" s="24" t="inlineStr">
+        <is>
+          <t>-0.915897</t>
+        </is>
+      </c>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="inlineStr">
+        <is>
+          <t>-5.749741</t>
+        </is>
+      </c>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="inlineStr">
+        <is>
+          <t>0.543228</t>
+        </is>
+      </c>
+      <c r="CS42" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>c2b8ff34971a4524</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:02:00.677208Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>401857134</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.601532</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.011368</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>106</v>
+      </c>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AD43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T02:05:35.184671Z</t>
+        </is>
+      </c>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5900 (aec-wnba-ny-ind-2026-08-11); model edge vs ask +0.0115. NOTE: NO_CALL_AVAILABILITY_PLAYER_UNMAPPED unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>wnba-ind</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>ba520a9a4c477ab6</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:01:21.703219Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN43" s="28" t="n">
+        <v>0.584158</v>
+      </c>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="inlineStr">
+        <is>
+          <t>0.6211005454</t>
+        </is>
+      </c>
+      <c r="CD43" s="24" t="inlineStr">
+        <is>
+          <t>-4.657768</t>
+        </is>
+      </c>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_PLAYER_UNMAPPED</t>
+        </is>
+      </c>
+      <c r="CJ43" s="24" t="inlineStr">
+        <is>
+          <t>-1.837931</t>
+        </is>
+      </c>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="inlineStr">
+        <is>
+          <t>0.601532</t>
+        </is>
+      </c>
+      <c r="CS43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>94b6e82d47414a9a</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:02:00.677208Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>401857135</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.607315</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>-0.112573</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="AD44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:11:32.121723Z</t>
+        </is>
+      </c>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7200 (aec-wnba-wsh-lv-2026-08-11); model edge vs ask -0.1127.</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>a0c31254ee1bbd66</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:01:22.435695Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="BN44" s="28" t="n">
+        <v>0.712871</v>
+      </c>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="inlineStr">
+        <is>
+          <t>0.6234716814</t>
+        </is>
+      </c>
+      <c r="CD44" s="24" t="inlineStr">
+        <is>
+          <t>-4.445907</t>
+        </is>
+      </c>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="inlineStr">
+        <is>
+          <t>-8.030375</t>
+        </is>
+      </c>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="inlineStr">
+        <is>
+          <t>0.607315</t>
+        </is>
+      </c>
+      <c r="CS44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>5996ca17401a4bdb</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:02:00.677208Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>401857136</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.605795</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>0.046324</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:11:32.639916Z</t>
+        </is>
+      </c>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-phx-la-2026-08-11); model edge vs ask +0.0458.</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>ea8ddf96e9d55211</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:01:23.084715Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN45" s="28" t="n">
+        <v>0.554455</v>
+      </c>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="inlineStr">
+        <is>
+          <t>0.6486314752</t>
+        </is>
+      </c>
+      <c r="CD45" s="24" t="inlineStr">
+        <is>
+          <t>2.704875</t>
+        </is>
+      </c>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="inlineStr">
+        <is>
+          <t>4.540233</t>
+        </is>
+      </c>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="inlineStr">
+        <is>
+          <t>0.605795</t>
+        </is>
+      </c>
+      <c r="CS45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>b2bf5cf7a91d4eaf</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:42:37.205703Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>401857137</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-426</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.234742</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.809886</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.752207</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>-0.057679</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n"/>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8100 (aec-wnba-tor-dal-2026-08-12); model edge vs ask -0.0578. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>bed262b4cc2cb026</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:29.908829Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n">
+        <v>-426</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.234742</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.809886</v>
+      </c>
+      <c r="BN46" s="28" t="n">
+        <v>0.80198</v>
+      </c>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="inlineStr">
+        <is>
+          <t>0.8593821994</t>
+        </is>
+      </c>
+      <c r="CD46" s="24" t="inlineStr">
+        <is>
+          <t>1.688216</t>
+        </is>
+      </c>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ46" s="24" t="inlineStr">
+        <is>
+          <t>0.008501</t>
+        </is>
+      </c>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="inlineStr">
+        <is>
+          <t>0.752207</t>
+        </is>
+      </c>
+      <c r="CS46" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>bfeeede986364356</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:42:37.205703Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>401857138</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.7756999999999999</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>-0.014216</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-chi-gsv-2026-08-12); model edge vs ask -0.0143.</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>25be967f882f1f6d</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:30.522789Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="BN47" s="28" t="n">
+        <v>0.782178</v>
+      </c>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="inlineStr">
+        <is>
+          <t>0.8909512632</t>
+        </is>
+      </c>
+      <c r="CD47" s="24" t="inlineStr">
+        <is>
+          <t>-3.866065</t>
+        </is>
+      </c>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="inlineStr">
+        <is>
+          <t>2.087162</t>
+        </is>
+      </c>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="inlineStr">
+        <is>
+          <t>0.7757</t>
+        </is>
+      </c>
+      <c r="CS47" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>562d72acc9a74e8f</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:42:37.205703Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>401857139</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.723101</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>-0.156851</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-min-por-2026-08-12); model edge vs ask -0.1569. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>wnba-por</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>54b300fef3816245</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:30.941772Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN48" s="28" t="n">
+        <v>0.871287</v>
+      </c>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="inlineStr">
+        <is>
+          <t>0.1965379833</t>
+        </is>
+      </c>
+      <c r="CD48" s="24" t="inlineStr">
+        <is>
+          <t>-1.095212</t>
+        </is>
+      </c>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ48" s="24" t="inlineStr">
+        <is>
+          <t>3.932321</t>
+        </is>
+      </c>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="inlineStr">
+        <is>
+          <t>0.723101</t>
+        </is>
+      </c>
+      <c r="CS48" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat/wnba.xlsx
+++ b/data/flat/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS48" headerRowCount="1">
-  <autoFilter ref="A1:CS48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS51" headerRowCount="1">
+  <autoFilter ref="A1:CS51"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$48)</f>
+        <f>COUNTA('Picks'!$A$2:$A$51)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$48,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$48,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$51,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")/(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")/(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$48)/SUM('Picks'!$BX$2:$BX$48),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$51)/SUM('Picks'!$BX$2:$BX$51),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$48)</f>
+        <f>SUM('Picks'!$BY$2:$BY$51)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$48,"&lt;&gt;",'Picks'!$AB$2:$AB$48),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$51,"&lt;&gt;",'Picks'!$AB$2:$AB$51),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$48,'Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$51,'Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS48"/>
+  <dimension ref="A1:CS51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8450,7 +8450,7 @@
         <v>4</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
       <c r="AC25" s="30" t="n">
-        <v>0</v>
+        <v>0.7511</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
         <is>
@@ -8502,7 +8502,11 @@
       </c>
       <c r="AH25" s="24" t="n"/>
       <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK25" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -8751,7 +8755,7 @@
         <v>9</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8779,7 +8783,7 @@
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
       <c r="AC26" s="30" t="n">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
         <is>
@@ -8803,7 +8807,11 @@
       </c>
       <c r="AH26" s="24" t="n"/>
       <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK26" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9052,7 +9060,7 @@
         <v>19</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -9080,7 +9088,7 @@
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
       <c r="AC27" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
         <is>
@@ -9104,7 +9112,11 @@
       </c>
       <c r="AH27" s="24" t="n"/>
       <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK27" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9353,7 +9365,7 @@
         <v>13</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -9381,7 +9393,7 @@
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
       <c r="AC28" s="30" t="n">
-        <v>0</v>
+        <v>0.7519</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
         <is>
@@ -9405,7 +9417,11 @@
       </c>
       <c r="AH28" s="24" t="n"/>
       <c r="AI28" s="31" t="n"/>
-      <c r="AJ28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK28" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9658,7 +9674,7 @@
         <v>45</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9686,7 +9702,7 @@
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
       <c r="AC29" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
         <is>
@@ -9710,7 +9726,11 @@
       </c>
       <c r="AH29" s="24" t="n"/>
       <c r="AI29" s="31" t="n"/>
-      <c r="AJ29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK29" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9963,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9991,7 +10011,7 @@
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
       <c r="AC30" s="30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
         <is>
@@ -10015,7 +10035,11 @@
       </c>
       <c r="AH30" s="24" t="n"/>
       <c r="AI30" s="31" t="n"/>
-      <c r="AJ30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK30" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -10268,7 +10292,7 @@
         <v>42</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -10296,7 +10320,7 @@
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
       <c r="AC31" s="30" t="n">
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
         <is>
@@ -10320,7 +10344,11 @@
       </c>
       <c r="AH31" s="24" t="n"/>
       <c r="AI31" s="31" t="n"/>
-      <c r="AJ31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK31" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -10573,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10601,7 +10629,7 @@
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
       <c r="AC32" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
         <is>
@@ -10625,7 +10653,11 @@
       </c>
       <c r="AH32" s="24" t="n"/>
       <c r="AI32" s="31" t="n"/>
-      <c r="AJ32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK32" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -11179,7 +11211,7 @@
         <v>31</v>
       </c>
       <c r="S34" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
@@ -11207,7 +11239,7 @@
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
       <c r="AC34" s="30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD34" s="24" t="inlineStr">
         <is>
@@ -11231,7 +11263,11 @@
       </c>
       <c r="AH34" s="24" t="n"/>
       <c r="AI34" s="31" t="n"/>
-      <c r="AJ34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK34" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -11480,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
@@ -11508,7 +11544,7 @@
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
       <c r="AC35" s="30" t="n">
-        <v>0</v>
+        <v>0.6726</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
         <is>
@@ -11532,7 +11568,11 @@
       </c>
       <c r="AH35" s="24" t="n"/>
       <c r="AI35" s="31" t="n"/>
-      <c r="AJ35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK35" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -12700,7 +12740,7 @@
         <v>22</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -12728,7 +12768,7 @@
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
       <c r="AC39" s="30" t="n">
-        <v>0</v>
+        <v>0.8969</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
         <is>
@@ -12752,7 +12792,11 @@
       </c>
       <c r="AH39" s="24" t="n"/>
       <c r="AI39" s="31" t="n"/>
-      <c r="AJ39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK39" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -14754,12 +14798,12 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>b2bf5cf7a91d4eaf</t>
+          <t>9a7140dd6ef9419e</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:42:37.205703Z</t>
+          <t>2026-08-12T21:16:50.725033Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -14832,18 +14876,32 @@
       </c>
       <c r="U46" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>94</v>
+      </c>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
+      <c r="AC46" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:37.822322Z</t>
+        </is>
+      </c>
       <c r="AE46" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.8100 (aec-wnba-tor-dal-2026-08-12); model edge vs ask -0.0578. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
@@ -14965,7 +15023,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:29.908829Z</t>
+          <t>2026-08-12T21:16:26.173511Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -15045,12 +15103,12 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>bfeeede986364356</t>
+          <t>c8cac0b239c94d4a</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:42:37.205703Z</t>
+          <t>2026-08-12T21:16:50.725033Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
@@ -15123,18 +15181,32 @@
       </c>
       <c r="U47" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>91</v>
+      </c>
       <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
+      <c r="AC47" s="30" t="n">
+        <v>0.5319</v>
+      </c>
+      <c r="AD47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:38.558633Z</t>
+        </is>
+      </c>
       <c r="AE47" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-chi-gsv-2026-08-12); model edge vs ask -0.0143.</t>
@@ -15256,7 +15328,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:30.522789Z</t>
+          <t>2026-08-12T21:16:26.781920Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15332,12 +15404,12 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>562d72acc9a74e8f</t>
+          <t>ee43dfb319904a55</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:42:37.205703Z</t>
+          <t>2026-08-12T21:16:50.725033Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -15382,20 +15454,20 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="O48" s="28" t="n">
         <v>0.723101</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>-0.156851</v>
+        <v>-0.136843</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>0</v>
@@ -15410,21 +15482,35 @@
       </c>
       <c r="U48" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W48" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>81</v>
+      </c>
       <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
+      <c r="AC48" s="30" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:39.125413Z</t>
+        </is>
+      </c>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-min-por-2026-08-12); model edge vs ask -0.1569. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8600 (aec-wnba-min-por-2026-08-12); model edge vs ask -0.1369. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -15543,7 +15629,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:30.941772Z</t>
+          <t>2026-08-12T21:16:27.215401Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -15553,16 +15639,16 @@
       </c>
       <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="BN48" s="28" t="n">
-        <v>0.871287</v>
+        <v>0.851485</v>
       </c>
       <c r="BO48" s="28" t="n"/>
       <c r="BP48" s="25" t="n"/>
@@ -15620,6 +15706,871 @@
         </is>
       </c>
     </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>8309e4105a6f4fc7</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:51.037990Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>401857140</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.6314380000000001</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>-0.188706</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8200 (aec-wnba-atl-conn-2026-08-13); model edge vs ask -0.1886. NOTE: NO_CALL_AVAILABILITY_PLAYER_UNMAPPED unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>wnba-con</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>eb693c1f8106b97c</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:45.049604Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="BN49" s="28" t="n">
+        <v>0.811881</v>
+      </c>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="inlineStr">
+        <is>
+          <t>0.3258499922</t>
+        </is>
+      </c>
+      <c r="CD49" s="24" t="inlineStr">
+        <is>
+          <t>-4.55436</t>
+        </is>
+      </c>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_PLAYER_UNMAPPED</t>
+        </is>
+      </c>
+      <c r="CJ49" s="24" t="inlineStr">
+        <is>
+          <t>6.374313</t>
+        </is>
+      </c>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="n"/>
+      <c r="CR49" s="24" t="inlineStr">
+        <is>
+          <t>0.631438</t>
+        </is>
+      </c>
+      <c r="CS49" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>449e0ae003a643a4</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:51.037990Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>401857141</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-355</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.28169</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.78022</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.70842</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>-0.0718</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7800 (aec-wnba-la-ny-2026-08-13); model edge vs ask -0.0716.</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>16b7a00d19006dde</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:45.988570Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n">
+        <v>-355</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>1.28169</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.78022</v>
+      </c>
+      <c r="BN50" s="28" t="n">
+        <v>0.772277</v>
+      </c>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="inlineStr">
+        <is>
+          <t>0.7947999616</t>
+        </is>
+      </c>
+      <c r="CD50" s="24" t="inlineStr">
+        <is>
+          <t>5.744366</t>
+        </is>
+      </c>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="inlineStr">
+        <is>
+          <t>-2.420027</t>
+        </is>
+      </c>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="n"/>
+      <c r="CR50" s="24" t="inlineStr">
+        <is>
+          <t>0.70842</t>
+        </is>
+      </c>
+      <c r="CS50" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>18b27f5a1d5f4ea6</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:51.037990Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>401857142</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.637269</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>-0.032698</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6700 (aec-wnba-wsh-lv-2026-08-13); model edge vs ask -0.0327.</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>ff96e0111a58886e</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:46.550249Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN51" s="28" t="n">
+        <v>0.663366</v>
+      </c>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="inlineStr">
+        <is>
+          <t>0.6691278675</t>
+        </is>
+      </c>
+      <c r="CD51" s="24" t="inlineStr">
+        <is>
+          <t>-3.282439</t>
+        </is>
+      </c>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="inlineStr">
+        <is>
+          <t>-5.390663</t>
+        </is>
+      </c>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="inlineStr">
+        <is>
+          <t>0.637269</t>
+        </is>
+      </c>
+      <c r="CS51" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
